--- a/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0003T0006Z000C1N16_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0003T0006Z000C1N16_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>38.91508246355457</v>
+        <v>6.323700900327617</v>
       </c>
       <c r="D2" t="n">
-        <v>43.79883755247978</v>
+        <v>7.117311102277965</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3052930407905</v>
+        <v>0.8621101191284563</v>
       </c>
       <c r="F2" t="n">
-        <v>14.19955967057814</v>
+        <v>2.307428446468947</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>31.31262897549217</v>
+        <v>5.088302208517478</v>
       </c>
       <c r="D3" t="n">
-        <v>14.95605243575749</v>
+        <v>2.430358520810592</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3052930407905</v>
+        <v>0.8621101191284563</v>
       </c>
       <c r="F3" t="n">
-        <v>14.19955967057814</v>
+        <v>2.307428446468947</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.09737161877853</v>
+        <v>6.190822888051511</v>
       </c>
       <c r="D4" t="n">
-        <v>11.1091731709054</v>
+        <v>1.805240640272128</v>
       </c>
       <c r="E4" t="n">
-        <v>5.3052930407905</v>
+        <v>0.8621101191284563</v>
       </c>
       <c r="F4" t="n">
-        <v>14.19955967057814</v>
+        <v>2.307428446468947</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>32.63415770765305</v>
+        <v>5.30305062749362</v>
       </c>
       <c r="D5" t="n">
-        <v>20.44589020020825</v>
+        <v>3.32245715753384</v>
       </c>
       <c r="E5" t="n">
-        <v>5.3052930407905</v>
+        <v>0.8621101191284563</v>
       </c>
       <c r="F5" t="n">
-        <v>14.19955967057814</v>
+        <v>2.307428446468947</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>24.31515012959436</v>
+        <v>3.951211896059084</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>0.8125</v>
       </c>
       <c r="E6" t="n">
-        <v>5.3052930407905</v>
+        <v>0.8621101191284563</v>
       </c>
       <c r="F6" t="n">
-        <v>14.19955967057814</v>
+        <v>2.307428446468947</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>22.2833693812853</v>
+        <v>3.621047524458861</v>
       </c>
       <c r="D7" t="n">
-        <v>38.06106807711055</v>
+        <v>6.184923562530465</v>
       </c>
       <c r="E7" t="n">
-        <v>5.3052930407905</v>
+        <v>0.8621101191284563</v>
       </c>
       <c r="F7" t="n">
-        <v>14.19955967057814</v>
+        <v>2.307428446468947</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>29.57884370539809</v>
+        <v>4.80656210212719</v>
       </c>
       <c r="D8" t="n">
-        <v>9.35102684196101</v>
+        <v>1.519541861818664</v>
       </c>
       <c r="E8" t="n">
-        <v>5.3052930407905</v>
+        <v>0.8621101191284563</v>
       </c>
       <c r="F8" t="n">
-        <v>14.19955967057814</v>
+        <v>2.307428446468947</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>30.26321537981216</v>
+        <v>4.917772499219477</v>
       </c>
       <c r="D9" t="n">
-        <v>20.93362489791074</v>
+        <v>3.401714045910495</v>
       </c>
       <c r="E9" t="n">
-        <v>5.3052930407905</v>
+        <v>0.8621101191284563</v>
       </c>
       <c r="F9" t="n">
-        <v>14.19955967057814</v>
+        <v>2.307428446468947</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>26.841504873688</v>
+        <v>4.3617445419743</v>
       </c>
       <c r="D10" t="n">
-        <v>51.16558812123291</v>
+        <v>8.314408069700349</v>
       </c>
       <c r="E10" t="n">
-        <v>5.3052930407905</v>
+        <v>0.8621101191284563</v>
       </c>
       <c r="F10" t="n">
-        <v>14.19955967057814</v>
+        <v>2.307428446468947</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>36.41300654740783</v>
+        <v>5.917113563953772</v>
       </c>
       <c r="D11" t="n">
-        <v>27.26786626388801</v>
+        <v>4.431028267881802</v>
       </c>
       <c r="E11" t="n">
-        <v>5.3052930407905</v>
+        <v>0.8621101191284563</v>
       </c>
       <c r="F11" t="n">
-        <v>14.19955967057814</v>
+        <v>2.307428446468947</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>25.92330143351089</v>
+        <v>4.21253648294552</v>
       </c>
       <c r="D12" t="n">
-        <v>18.05838560899134</v>
+        <v>2.934487661461093</v>
       </c>
       <c r="E12" t="n">
-        <v>5.3052930407905</v>
+        <v>0.8621101191284563</v>
       </c>
       <c r="F12" t="n">
-        <v>14.19955967057814</v>
+        <v>2.307428446468947</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
